--- a/planning/sales_approval/D251231-01_주니파이커넥트(조립PC)_품의서 예시 파일.xlsx
+++ b/planning/sales_approval/D251231-01_주니파이커넥트(조립PC)_품의서 예시 파일.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DHKIM\Desktop\김대훈\ME\파트 품의서\파트 품의서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jangjingang/dev/smerp_next/planning/sales_approval/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1035C6-F53A-4217-A582-CBD1B4F84AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D5EBC2-BB1A-9D44-BE8D-C55B0188151B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="2490" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SALES" sheetId="2" r:id="rId1"/>
@@ -18,10 +18,21 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SALES!$B$2:$M$42</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -319,10 +330,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -934,17 +945,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1025,7 +1036,7 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1085,7 +1096,7 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="26" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1094,7 +1105,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1109,64 +1120,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="4" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="4" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="24" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="19" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="20" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="15" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="15" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="4" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="4" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="23" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="24" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="23" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="24" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1175,49 +1186,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="5" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="5" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="18" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="18" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="21" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="21" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="5" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="5" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="24" fillId="5" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="19" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="5" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="19" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="22" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="22" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1226,22 +1237,22 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="24" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="24" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1259,10 +1270,10 @@
     <xf numFmtId="0" fontId="24" fillId="6" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="24" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="24" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="24" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="24" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="5" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1630,24 +1641,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:P42"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="76.1640625" customWidth="1"/>
-    <col min="5" max="5" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="52" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="52" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.58203125" customWidth="1"/>
-    <col min="9" max="10" width="16.58203125" customWidth="1"/>
-    <col min="11" max="11" width="16.58203125" style="52" customWidth="1"/>
-    <col min="12" max="12" width="17.25" style="52" customWidth="1"/>
+    <col min="7" max="7" width="15.1640625" style="52" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5" customWidth="1"/>
+    <col min="9" max="10" width="16.5" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="52" customWidth="1"/>
+    <col min="12" max="12" width="17.1640625" style="52" customWidth="1"/>
     <col min="13" max="13" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="17.5" thickBot="1"/>
+    <row r="1" spans="2:13" ht="18" thickBot="1"/>
     <row r="2" spans="2:13">
       <c r="B2" s="17"/>
       <c r="C2" s="18"/>
@@ -1720,7 +1731,7 @@
       <c r="L6" s="98"/>
       <c r="M6" s="20"/>
     </row>
-    <row r="7" spans="2:13" ht="39.5">
+    <row r="7" spans="2:13" ht="40">
       <c r="B7" s="12"/>
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
@@ -1734,7 +1745,7 @@
       <c r="L7" s="55"/>
       <c r="M7" s="20"/>
     </row>
-    <row r="8" spans="2:13" ht="17.5">
+    <row r="8" spans="2:13" ht="18">
       <c r="B8" s="12"/>
       <c r="C8" s="36" t="s">
         <v>23</v>
@@ -1750,7 +1761,7 @@
       <c r="L8" s="56"/>
       <c r="M8" s="20"/>
     </row>
-    <row r="9" spans="2:13" ht="17.5">
+    <row r="9" spans="2:13" ht="18">
       <c r="B9" s="12"/>
       <c r="C9" s="28" t="s">
         <v>18</v>
@@ -1768,7 +1779,7 @@
       <c r="L9" s="56"/>
       <c r="M9" s="20"/>
     </row>
-    <row r="10" spans="2:13" ht="17.5">
+    <row r="10" spans="2:13" ht="18">
       <c r="B10" s="12"/>
       <c r="C10" s="28" t="s">
         <v>19</v>
@@ -1786,7 +1797,7 @@
       <c r="L10" s="56"/>
       <c r="M10" s="20"/>
     </row>
-    <row r="11" spans="2:13" ht="17.5">
+    <row r="11" spans="2:13" ht="18">
       <c r="B11" s="12"/>
       <c r="C11" s="28" t="s">
         <v>20</v>
@@ -1854,7 +1865,7 @@
       <c r="L14" s="75"/>
       <c r="M14" s="20"/>
     </row>
-    <row r="15" spans="2:13" ht="18" thickBot="1">
+    <row r="15" spans="2:13" ht="19" thickBot="1">
       <c r="B15" s="12"/>
       <c r="C15" s="28" t="s">
         <v>29</v>
@@ -1872,7 +1883,7 @@
       <c r="L15" s="80"/>
       <c r="M15" s="20"/>
     </row>
-    <row r="16" spans="2:13" ht="18" thickBot="1">
+    <row r="16" spans="2:13" ht="20" thickBot="1">
       <c r="B16" s="12"/>
       <c r="C16" s="13" t="s">
         <v>1</v>
@@ -1926,7 +1937,7 @@
       <c r="L17" s="82"/>
       <c r="M17" s="20"/>
     </row>
-    <row r="18" spans="2:16">
+    <row r="18" spans="2:16" ht="18">
       <c r="B18" s="12"/>
       <c r="C18" s="50" t="s">
         <v>35</v>
@@ -1957,7 +1968,7 @@
       </c>
       <c r="M18" s="82"/>
     </row>
-    <row r="19" spans="2:16">
+    <row r="19" spans="2:16" ht="18">
       <c r="B19" s="12"/>
       <c r="C19" s="50" t="s">
         <v>36</v>
@@ -1988,7 +1999,7 @@
       </c>
       <c r="M19" s="82"/>
     </row>
-    <row r="20" spans="2:16">
+    <row r="20" spans="2:16" ht="18">
       <c r="B20" s="12"/>
       <c r="C20" s="50" t="s">
         <v>40</v>
@@ -2020,7 +2031,7 @@
       <c r="M20" s="82"/>
       <c r="N20" s="91"/>
     </row>
-    <row r="21" spans="2:16">
+    <row r="21" spans="2:16" ht="18">
       <c r="B21" s="12"/>
       <c r="C21" s="50" t="s">
         <v>48</v>
@@ -2051,7 +2062,7 @@
       </c>
       <c r="M21" s="82"/>
     </row>
-    <row r="22" spans="2:16">
+    <row r="22" spans="2:16" ht="18">
       <c r="B22" s="12"/>
       <c r="C22" s="50" t="s">
         <v>48</v>
@@ -2082,7 +2093,7 @@
       </c>
       <c r="M22" s="82"/>
     </row>
-    <row r="23" spans="2:16">
+    <row r="23" spans="2:16" ht="18">
       <c r="B23" s="12"/>
       <c r="C23" s="50" t="s">
         <v>49</v>
@@ -2113,7 +2124,7 @@
       </c>
       <c r="M23" s="82"/>
     </row>
-    <row r="24" spans="2:16">
+    <row r="24" spans="2:16" ht="18">
       <c r="B24" s="12"/>
       <c r="C24" s="50" t="s">
         <v>38</v>
@@ -2144,7 +2155,7 @@
       </c>
       <c r="M24" s="82"/>
     </row>
-    <row r="25" spans="2:16">
+    <row r="25" spans="2:16" ht="18">
       <c r="B25" s="12"/>
       <c r="C25" s="50" t="s">
         <v>37</v>
@@ -2175,7 +2186,7 @@
       </c>
       <c r="M25" s="82"/>
     </row>
-    <row r="26" spans="2:16">
+    <row r="26" spans="2:16" ht="18">
       <c r="B26" s="12"/>
       <c r="C26" s="50" t="s">
         <v>41</v>
@@ -2206,7 +2217,7 @@
       </c>
       <c r="M26" s="82"/>
     </row>
-    <row r="27" spans="2:16">
+    <row r="27" spans="2:16" ht="18">
       <c r="B27" s="12"/>
       <c r="C27" s="50" t="s">
         <v>50</v>
@@ -2237,7 +2248,7 @@
       </c>
       <c r="M27" s="82"/>
     </row>
-    <row r="28" spans="2:16" ht="17.5" thickBot="1">
+    <row r="28" spans="2:16" ht="18" thickBot="1">
       <c r="B28" s="12"/>
       <c r="C28" s="50"/>
       <c r="D28" s="90"/>
@@ -2251,7 +2262,7 @@
       <c r="M28" s="82"/>
       <c r="P28" s="86"/>
     </row>
-    <row r="29" spans="2:16" ht="21.5" thickBot="1">
+    <row r="29" spans="2:16" ht="21" thickBot="1">
       <c r="B29" s="12"/>
       <c r="C29" s="100" t="s">
         <v>9</v>
@@ -2276,7 +2287,7 @@
       <c r="M29" s="47"/>
       <c r="N29" s="86"/>
     </row>
-    <row r="30" spans="2:16" ht="21.5" thickBot="1">
+    <row r="30" spans="2:16" ht="21" thickBot="1">
       <c r="B30" s="12"/>
       <c r="C30" s="49"/>
       <c r="D30" s="49"/>
@@ -2295,7 +2306,7 @@
       </c>
       <c r="M30" s="47"/>
     </row>
-    <row r="31" spans="2:16" ht="17.5">
+    <row r="31" spans="2:16" ht="19">
       <c r="B31" s="12"/>
       <c r="C31" s="21" t="s">
         <v>30</v>
@@ -2313,7 +2324,7 @@
       <c r="L31" s="108"/>
       <c r="M31" s="20"/>
     </row>
-    <row r="32" spans="2:16" ht="17.5">
+    <row r="32" spans="2:16" ht="19">
       <c r="B32" s="12"/>
       <c r="C32" s="37" t="s">
         <v>24</v>
@@ -2329,7 +2340,7 @@
       <c r="L32" s="77"/>
       <c r="M32" s="20"/>
     </row>
-    <row r="33" spans="2:16" ht="17.5">
+    <row r="33" spans="2:16" ht="19">
       <c r="B33" s="12"/>
       <c r="C33" s="33" t="s">
         <v>11</v>
@@ -2347,7 +2358,7 @@
       <c r="L33" s="108"/>
       <c r="M33" s="20"/>
     </row>
-    <row r="34" spans="2:16" ht="17.5">
+    <row r="34" spans="2:16" ht="19">
       <c r="B34" s="12"/>
       <c r="C34" s="33" t="s">
         <v>27</v>
@@ -2365,7 +2376,7 @@
       <c r="L34" s="63"/>
       <c r="M34" s="20"/>
     </row>
-    <row r="35" spans="2:16" ht="17.5">
+    <row r="35" spans="2:16" ht="18">
       <c r="B35" s="12"/>
       <c r="C35" s="33"/>
       <c r="D35" s="10"/>
@@ -2379,7 +2390,7 @@
       <c r="L35" s="63"/>
       <c r="M35" s="20"/>
     </row>
-    <row r="36" spans="2:16" ht="17.5">
+    <row r="36" spans="2:16" ht="19">
       <c r="B36" s="12"/>
       <c r="C36" s="33" t="s">
         <v>21</v>
@@ -2397,7 +2408,7 @@
       <c r="L36" s="63"/>
       <c r="M36" s="20"/>
     </row>
-    <row r="37" spans="2:16" ht="17.5">
+    <row r="37" spans="2:16" ht="19">
       <c r="B37" s="12"/>
       <c r="C37" s="34" t="s">
         <v>22</v>
@@ -2415,7 +2426,7 @@
       <c r="L37" s="63"/>
       <c r="M37" s="20"/>
     </row>
-    <row r="38" spans="2:16" ht="17.5">
+    <row r="38" spans="2:16" ht="19">
       <c r="B38" s="12"/>
       <c r="C38" s="34" t="s">
         <v>12</v>
@@ -2433,7 +2444,7 @@
       <c r="L38" s="63"/>
       <c r="M38" s="20"/>
     </row>
-    <row r="39" spans="2:16" ht="18" thickBot="1">
+    <row r="39" spans="2:16" ht="19" thickBot="1">
       <c r="B39" s="12"/>
       <c r="C39" s="22"/>
       <c r="D39" s="96"/>
@@ -2489,7 +2500,7 @@
       <c r="L41" s="85"/>
       <c r="M41" s="20"/>
     </row>
-    <row r="42" spans="2:16" ht="17.5" thickBot="1">
+    <row r="42" spans="2:16" ht="18" thickBot="1">
       <c r="B42" s="14"/>
       <c r="C42" s="15"/>
       <c r="D42" s="15"/>
